--- a/Submissions/GroupFormation/STA380GroupForm.xlsx
+++ b/Submissions/GroupFormation/STA380GroupForm.xlsx
@@ -5,12 +5,12 @@
   <workbookPr/>
   <mc:AlternateContent xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006">
     <mc:Choice Requires="x15">
-      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADEus\Downloads\"/>
+      <x15ac:absPath xmlns:x15ac="http://schemas.microsoft.com/office/spreadsheetml/2010/11/ac" url="C:\Users\ADEus\OneDrive\Desktop\AKMproject\Submissions\GroupFormation\"/>
     </mc:Choice>
   </mc:AlternateContent>
-  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{97415F96-55FE-4146-9724-C6B187C0599B}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
+  <xr:revisionPtr revIDLastSave="0" documentId="13_ncr:1_{5552D12D-EF33-4A7C-ADCC-22197CE5CF7C}" xr6:coauthVersionLast="47" xr6:coauthVersionMax="47" xr10:uidLastSave="{00000000-0000-0000-0000-000000000000}"/>
   <bookViews>
-    <workbookView xWindow="10980" yWindow="2570" windowWidth="21860" windowHeight="13830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
+    <workbookView xWindow="8850" yWindow="5270" windowWidth="21860" windowHeight="13830" xr2:uid="{00000000-000D-0000-FFFF-FFFF00000000}"/>
   </bookViews>
   <sheets>
     <sheet name="Sheet1" sheetId="1" r:id="rId1"/>
@@ -20,7 +20,7 @@
 </file>
 
 <file path=xl/sharedStrings.xml><?xml version="1.0" encoding="utf-8"?>
-<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="39" uniqueCount="35">
+<sst xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" count="50" uniqueCount="47">
   <si>
     <t>If left blank, you will be assigned a number.</t>
   </si>
@@ -137,6 +137,54 @@
   </si>
   <si>
     <t>AKM</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Simulated distributions, if applicable:</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Interactive Monte Carlo Analysis of the Bias-Variance Tradeoff in Regression Models (Original)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Noise distribution: Normal N(0, σ^2)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Use Monte Carlo simulation to repeatedly generate training and test datasets</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Compare regression models with varying complexity, including polynomial regression and kNN regression.</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Estimate training error, test error, and Monte Carlo approximations of bias^2 and variance</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Develop an interactive R Shiny application allowing users to adjust sample size, noise level, model type, and model complexity</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Core simulation functions will be packaged as an R package with unit tests writing using testthat</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Monte Carlo Simulation of a Hypothesis Test (Topic 5)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Normal distribution</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>Bootstrap Confidence Interval (Topic 10)</t>
+    <phoneticPr fontId="4" type="noConversion"/>
+  </si>
+  <si>
+    <t>N/A</t>
     <phoneticPr fontId="4" type="noConversion"/>
   </si>
 </sst>
@@ -144,7 +192,7 @@
 
 <file path=xl/styles.xml><?xml version="1.0" encoding="utf-8"?>
 <styleSheet xmlns="http://schemas.openxmlformats.org/spreadsheetml/2006/main" xmlns:mc="http://schemas.openxmlformats.org/markup-compatibility/2006" xmlns:x14ac="http://schemas.microsoft.com/office/spreadsheetml/2009/9/ac" xmlns:x16r2="http://schemas.microsoft.com/office/spreadsheetml/2015/02/main" xmlns:xr="http://schemas.microsoft.com/office/spreadsheetml/2014/revision" mc:Ignorable="x14ac x16r2 xr">
-  <fonts count="7" x14ac:knownFonts="1">
+  <fonts count="8" x14ac:knownFonts="1">
     <font>
       <sz val="10"/>
       <color rgb="FF000000"/>
@@ -194,6 +242,14 @@
       <family val="2"/>
       <scheme val="minor"/>
     </font>
+    <font>
+      <b/>
+      <sz val="10"/>
+      <color theme="1"/>
+      <name val="Arial"/>
+      <family val="2"/>
+      <scheme val="minor"/>
+    </font>
   </fonts>
   <fills count="3">
     <fill>
@@ -222,7 +278,7 @@
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" applyNumberFormat="0" applyFill="0" applyBorder="0" applyAlignment="0" applyProtection="0"/>
   </cellStyleXfs>
-  <cellXfs count="7">
+  <cellXfs count="8">
     <xf numFmtId="0" fontId="0" fillId="0" borderId="0" xfId="0"/>
     <xf numFmtId="0" fontId="1" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
     <xf numFmtId="0" fontId="2" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
@@ -230,6 +286,7 @@
     <xf numFmtId="0" fontId="1" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="5" fillId="0" borderId="0" xfId="0" applyFont="1"/>
     <xf numFmtId="0" fontId="6" fillId="0" borderId="0" xfId="1"/>
+    <xf numFmtId="0" fontId="7" fillId="2" borderId="0" xfId="0" applyFont="1" applyFill="1"/>
   </cellXfs>
   <cellStyles count="2">
     <cellStyle name="常规" xfId="0" builtinId="0"/>
@@ -449,7 +506,7 @@
   <sheetPr>
     <outlinePr summaryBelow="0" summaryRight="0"/>
   </sheetPr>
-  <dimension ref="A1:F30"/>
+  <dimension ref="A1:F33"/>
   <sheetFormatPr defaultColWidth="12.6328125" defaultRowHeight="15.75" customHeight="1" x14ac:dyDescent="0.25"/>
   <cols>
     <col min="1" max="1" width="31.6328125" customWidth="1"/>
@@ -488,176 +545,218 @@
       <c r="A5" s="3" t="s">
         <v>3</v>
       </c>
+      <c r="B5" s="5" t="s">
+        <v>36</v>
+      </c>
     </row>
     <row r="6" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A6" s="3" t="s">
-        <v>4</v>
+      <c r="A6" s="7" t="s">
+        <v>35</v>
+      </c>
+      <c r="B6" s="5" t="s">
+        <v>37</v>
       </c>
     </row>
     <row r="7" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A7" s="3" t="s">
         <v>5</v>
       </c>
+      <c r="B7" s="5" t="s">
+        <v>38</v>
+      </c>
     </row>
     <row r="8" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A8" s="3"/>
+      <c r="B8" s="5" t="s">
+        <v>39</v>
+      </c>
     </row>
     <row r="9" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A9" s="3"/>
+      <c r="B9" s="5" t="s">
+        <v>40</v>
+      </c>
     </row>
     <row r="10" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A10" s="3" t="s">
+      <c r="A10" s="3"/>
+      <c r="B10" s="5" t="s">
+        <v>41</v>
+      </c>
+    </row>
+    <row r="11" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="A11" s="3"/>
+      <c r="B11" s="5" t="s">
+        <v>42</v>
+      </c>
+    </row>
+    <row r="12" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="A12" s="3"/>
+    </row>
+    <row r="13" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="A13" s="3" t="s">
         <v>6</v>
       </c>
-    </row>
-    <row r="11" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A11" s="3" t="s">
+      <c r="B13" s="5" t="s">
+        <v>43</v>
+      </c>
+    </row>
+    <row r="14" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="A14" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="12" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A12" s="3" t="s">
-        <v>5</v>
-      </c>
-    </row>
-    <row r="13" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A13" s="3"/>
-    </row>
-    <row r="14" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A14" s="3"/>
+      <c r="B14" s="5" t="s">
+        <v>44</v>
+      </c>
     </row>
     <row r="15" spans="1:4" ht="13" x14ac:dyDescent="0.3">
       <c r="A15" s="3" t="s">
+        <v>5</v>
+      </c>
+    </row>
+    <row r="16" spans="1:4" ht="13" x14ac:dyDescent="0.3">
+      <c r="A16" s="3"/>
+    </row>
+    <row r="17" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="A17" s="3"/>
+    </row>
+    <row r="18" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="A18" s="3" t="s">
         <v>7</v>
       </c>
-    </row>
-    <row r="16" spans="1:4" ht="13" x14ac:dyDescent="0.3">
-      <c r="A16" s="3" t="s">
+      <c r="B18" s="5" t="s">
+        <v>45</v>
+      </c>
+    </row>
+    <row r="19" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="A19" s="3" t="s">
         <v>4</v>
       </c>
-    </row>
-    <row r="17" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A17" s="3" t="s">
+      <c r="B19" s="5" t="s">
+        <v>46</v>
+      </c>
+    </row>
+    <row r="20" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="A20" s="3" t="s">
         <v>5</v>
       </c>
     </row>
-    <row r="18" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A18" s="3"/>
-    </row>
-    <row r="20" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A20" s="1"/>
-      <c r="B20" s="3" t="s">
+    <row r="21" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="A21" s="3"/>
+    </row>
+    <row r="23" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="A23" s="1"/>
+      <c r="B23" s="3" t="s">
         <v>8</v>
       </c>
-      <c r="C20" s="3" t="s">
+      <c r="C23" s="3" t="s">
         <v>9</v>
       </c>
-      <c r="D20" s="3" t="s">
+      <c r="D23" s="3" t="s">
         <v>10</v>
       </c>
-      <c r="E20" s="3" t="s">
+      <c r="E23" s="3" t="s">
         <v>11</v>
       </c>
-      <c r="F20" s="3" t="s">
+      <c r="F23" s="3" t="s">
         <v>12</v>
-      </c>
-    </row>
-    <row r="21" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A21" s="3" t="s">
-        <v>13</v>
-      </c>
-      <c r="B21" s="5" t="s">
-        <v>22</v>
-      </c>
-      <c r="C21" s="5" t="s">
-        <v>23</v>
-      </c>
-      <c r="D21">
-        <v>1009958958</v>
-      </c>
-      <c r="E21" s="5" t="s">
-        <v>24</v>
-      </c>
-      <c r="F21" s="6" t="s">
-        <v>29</v>
-      </c>
-    </row>
-    <row r="22" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A22" s="3" t="s">
-        <v>14</v>
-      </c>
-      <c r="B22" s="5" t="s">
-        <v>25</v>
-      </c>
-      <c r="C22" s="5" t="s">
-        <v>26</v>
-      </c>
-      <c r="D22">
-        <v>1009835458</v>
-      </c>
-      <c r="E22" s="5" t="s">
-        <v>27</v>
-      </c>
-      <c r="F22" s="6" t="s">
-        <v>28</v>
-      </c>
-    </row>
-    <row r="23" spans="1:6" ht="13" x14ac:dyDescent="0.3">
-      <c r="A23" s="3" t="s">
-        <v>15</v>
-      </c>
-      <c r="B23" s="5" t="s">
-        <v>31</v>
-      </c>
-      <c r="C23" s="5" t="s">
-        <v>30</v>
-      </c>
-      <c r="D23">
-        <v>1010443691</v>
-      </c>
-      <c r="E23" s="5" t="s">
-        <v>32</v>
-      </c>
-      <c r="F23" s="6" t="s">
-        <v>33</v>
       </c>
     </row>
     <row r="24" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A24" s="3" t="s">
-        <v>16</v>
+        <v>13</v>
+      </c>
+      <c r="B24" s="5" t="s">
+        <v>22</v>
+      </c>
+      <c r="C24" s="5" t="s">
+        <v>23</v>
+      </c>
+      <c r="D24">
+        <v>1009958958</v>
+      </c>
+      <c r="E24" s="5" t="s">
+        <v>24</v>
+      </c>
+      <c r="F24" s="6" t="s">
+        <v>29</v>
       </c>
     </row>
     <row r="25" spans="1:6" ht="13" x14ac:dyDescent="0.3">
       <c r="A25" s="3" t="s">
+        <v>14</v>
+      </c>
+      <c r="B25" s="5" t="s">
+        <v>25</v>
+      </c>
+      <c r="C25" s="5" t="s">
+        <v>26</v>
+      </c>
+      <c r="D25">
+        <v>1009835458</v>
+      </c>
+      <c r="E25" s="5" t="s">
+        <v>27</v>
+      </c>
+      <c r="F25" s="6" t="s">
+        <v>28</v>
+      </c>
+    </row>
+    <row r="26" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="A26" s="3" t="s">
+        <v>15</v>
+      </c>
+      <c r="B26" s="5" t="s">
+        <v>31</v>
+      </c>
+      <c r="C26" s="5" t="s">
+        <v>30</v>
+      </c>
+      <c r="D26">
+        <v>1010443691</v>
+      </c>
+      <c r="E26" s="5" t="s">
+        <v>32</v>
+      </c>
+      <c r="F26" s="6" t="s">
+        <v>33</v>
+      </c>
+    </row>
+    <row r="27" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="A27" s="3" t="s">
+        <v>16</v>
+      </c>
+    </row>
+    <row r="28" spans="1:6" ht="13" x14ac:dyDescent="0.3">
+      <c r="A28" s="3" t="s">
         <v>17</v>
-      </c>
-    </row>
-    <row r="27" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A27" s="4" t="s">
-        <v>18</v>
-      </c>
-    </row>
-    <row r="28" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A28" s="4" t="s">
-        <v>19</v>
-      </c>
-    </row>
-    <row r="29" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
-      <c r="A29" s="4" t="s">
-        <v>20</v>
       </c>
     </row>
     <row r="30" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
       <c r="A30" s="4" t="s">
+        <v>18</v>
+      </c>
+    </row>
+    <row r="31" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A31" s="4" t="s">
+        <v>19</v>
+      </c>
+    </row>
+    <row r="32" spans="1:6" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A32" s="4" t="s">
+        <v>20</v>
+      </c>
+    </row>
+    <row r="33" spans="1:1" ht="15.75" customHeight="1" x14ac:dyDescent="0.25">
+      <c r="A33" s="4" t="s">
         <v>21</v>
       </c>
     </row>
   </sheetData>
   <phoneticPr fontId="4" type="noConversion"/>
   <hyperlinks>
-    <hyperlink ref="F22" r:id="rId1" xr:uid="{0088D8B4-0FCD-4A9E-B4E1-6C374747C4E5}"/>
-    <hyperlink ref="F21" r:id="rId2" xr:uid="{EA21D6C9-549A-4BEE-B984-D515F03DE923}"/>
-    <hyperlink ref="F23" r:id="rId3" xr:uid="{48ACB30C-706E-4B47-AA85-211577445C3C}"/>
+    <hyperlink ref="F25" r:id="rId1" xr:uid="{0088D8B4-0FCD-4A9E-B4E1-6C374747C4E5}"/>
+    <hyperlink ref="F24" r:id="rId2" xr:uid="{EA21D6C9-549A-4BEE-B984-D515F03DE923}"/>
+    <hyperlink ref="F26" r:id="rId3" xr:uid="{48ACB30C-706E-4B47-AA85-211577445C3C}"/>
   </hyperlinks>
   <pageMargins left="0.7" right="0.7" top="0.75" bottom="0.75" header="0.3" footer="0.3"/>
 </worksheet>
